--- a/Source_Data.xlsx
+++ b/Source_Data.xlsx
@@ -830,7 +830,7 @@
         <v>0.002263103458721716</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06871602063158783</v>
+        <v>0.06884952128720195</v>
       </c>
       <c r="D2" t="n">
         <v>590</v>
@@ -852,10 +852,10 @@
         <v>0.002117764705670593</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01776209622083104</v>
+        <v>0.01793006064507883</v>
       </c>
       <c r="D3" t="n">
-        <v>7653.089873999999</v>
+        <v>12191.25990994771</v>
       </c>
       <c r="E3" t="n">
         <v>0.001269778531743261</v>
@@ -864,16 +864,16 @@
         <v>0.003962613216382103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009863726585278258</v>
+        <v>0.0100252989463729</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03174847599774792</v>
+        <v>0.03193038036053411</v>
       </c>
       <c r="I3" t="n">
-        <v>3167.649748</v>
+        <v>3094.649741172791</v>
       </c>
       <c r="J3" t="n">
-        <v>12138.53</v>
+        <v>21340.59976935387</v>
       </c>
     </row>
     <row r="4">
@@ -904,10 +904,10 @@
         <v>26.87325854076248</v>
       </c>
       <c r="C5" t="n">
-        <v>44.94682669335663</v>
+        <v>44.35256530000485</v>
       </c>
       <c r="D5" t="n">
-        <v>3414178773.126534</v>
+        <v>3154012306.778911</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -926,10 +926,10 @@
         <v>34.23216946127282</v>
       </c>
       <c r="C6" t="n">
-        <v>47.06389967847252</v>
+        <v>46.48448414237567</v>
       </c>
       <c r="D6" t="n">
-        <v>5044081470.875386</v>
+        <v>4696813960.444774</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -948,10 +948,10 @@
         <v>48.3707159399376</v>
       </c>
       <c r="C7" t="n">
-        <v>54.28443105166888</v>
+        <v>53.81360211389838</v>
       </c>
       <c r="D7" t="n">
-        <v>9605729803.472935</v>
+        <v>8975320466.222982</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
